--- a/data/source/weekly/cs-en-us-070pct.xlsx
+++ b/data/source/weekly/cs-en-us-070pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -904,11 +904,11 @@
       <c r="F15" s="15">
         <v>1</v>
       </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
-        <v>0</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="15">
         <v>1</v>
@@ -923,51 +923,51 @@
         <v>21</v>
       </c>
       <c r="M15" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N15" s="14">
-        <v>-91.666666666666</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F16" s="15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G16" s="15">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H16" s="14">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="I16" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J16" s="15">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K16" s="14">
-        <v>-36</v>
+        <v>-41.935483870967</v>
       </c>
       <c r="L16" s="14">
-        <v>-15.789473684210</v>
+        <v>-28</v>
       </c>
       <c r="M16" s="14">
-        <v>-36</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="N16" s="14">
-        <v>-93.6</v>
+        <v>-93.478260869565</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E17" s="14">
-        <v>-71.428571428571</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="F17" s="15">
         <v>13</v>
       </c>
       <c r="G17" s="15">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H17" s="14">
-        <v>-50</v>
+        <v>-56.666666666666</v>
       </c>
       <c r="I17" s="15">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J17" s="15">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="K17" s="14">
-        <v>-33.333333333333</v>
+        <v>-40.384615384615</v>
       </c>
       <c r="L17" s="14">
-        <v>-10.344827586206</v>
+        <v>-24.390243902439</v>
       </c>
       <c r="M17" s="14">
-        <v>-33.333333333333</v>
+        <v>-31.111111111111</v>
       </c>
       <c r="N17" s="14">
-        <v>-67.901234567901</v>
+        <v>-68.686868686868</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G18" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H18" s="14">
-        <v>-71.428571428571</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J18" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K18" s="14">
-        <v>-44.444444444444</v>
+        <v>-25</v>
       </c>
       <c r="L18" s="14">
-        <v>-61.538461538461</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M18" s="14">
-        <v>-81.481481481481</v>
+        <v>-70</v>
       </c>
       <c r="N18" s="14">
-        <v>-98.670212765957</v>
+        <v>-97.931034482758</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" s="15">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E19" s="14">
-        <v>50</v>
+        <v>333.333333333333</v>
       </c>
       <c r="F19" s="15">
+        <v>36</v>
+      </c>
+      <c r="G19" s="15">
         <v>28</v>
       </c>
-      <c r="G19" s="15">
-        <v>30</v>
-      </c>
       <c r="H19" s="14">
-        <v>-6.666666666666</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I19" s="15">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="J19" s="15">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K19" s="14">
-        <v>-9.756097560975</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L19" s="14">
-        <v>-11.904761904761</v>
+        <v>-4</v>
       </c>
       <c r="M19" s="14">
-        <v>-38.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="N19" s="14">
-        <v>-65.094339622641</v>
+        <v>-60.330578512396</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>4</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="F20" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G20" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H20" s="14">
-        <v>-14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="I20" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J20" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="14">
-        <v>-25</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L20" s="14">
-        <v>-53.846153846153</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="M20" s="14">
-        <v>-72.727272727272</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="N20" s="14">
-        <v>-97.785977859778</v>
+        <v>-96.855345911949</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D21" s="17">
         <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>-46.153846153846</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G21" s="17">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H21" s="18">
-        <v>-30.232558139534</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="I21" s="17">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="J21" s="17">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="K21" s="18">
-        <v>-26.016260162601</v>
+        <v>-21.476510067114</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.551724137931</v>
+        <v>-19.863013698630</v>
       </c>
       <c r="M21" s="18">
-        <v>-48</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="N21" s="18">
-        <v>-91.749773345421</v>
+        <v>-90.794649881982</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="15">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
       </c>
       <c r="F22" s="15">
+        <v>2</v>
+      </c>
+      <c r="G22" s="15">
         <v>1</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="H22" s="14">
+        <v>100</v>
       </c>
       <c r="I22" s="15">
-        <v>3</v>
-      </c>
-      <c r="J22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="J22" s="15">
+        <v>1</v>
+      </c>
+      <c r="K22" s="14">
+        <v>300</v>
       </c>
       <c r="L22" s="14">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M22" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D24" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E24" s="14">
-        <v>25</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F24" s="15">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G24" s="15">
         <v>87</v>
       </c>
       <c r="H24" s="14">
-        <v>-13.793103448275</v>
+        <v>-18.390804597701</v>
       </c>
       <c r="I24" s="15">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="J24" s="15">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="K24" s="14">
-        <v>-23.021582733812</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="L24" s="14">
-        <v>-44.845360824742</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="M24" s="14">
-        <v>-14.4</v>
+        <v>-13.698630136986</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D25" s="15">
         <v>9</v>
       </c>
       <c r="E25" s="14">
-        <v>-55.555555555555</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F25" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G25" s="15">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H25" s="14">
-        <v>-63.461538461538</v>
+        <v>-56.521739130434</v>
       </c>
       <c r="I25" s="15">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J25" s="15">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="K25" s="14">
-        <v>-71.264367816091</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L25" s="14">
-        <v>-78.991596638655</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F26" s="15">
         <v>40</v>
       </c>
       <c r="G26" s="15">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H26" s="14">
-        <v>21.212121212121</v>
+        <v>8.108108108108</v>
       </c>
       <c r="I26" s="15">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="J26" s="15">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K26" s="14">
-        <v>32.075471698113</v>
+        <v>23.809523809523</v>
       </c>
       <c r="L26" s="14">
-        <v>16.666666666666</v>
+        <v>5.405405405405</v>
       </c>
       <c r="M26" s="14">
-        <v>-16.666666666666</v>
+        <v>-20.408163265306</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1396,11 +1396,11 @@
       <c r="F27" s="15">
         <v>1</v>
       </c>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
-      <c r="H27" s="14">
-        <v>0</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="15">
         <v>1</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="15">
+        <v>4</v>
+      </c>
+      <c r="G28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="15">
-        <v>2</v>
-      </c>
-      <c r="G28" s="15">
-        <v>3</v>
-      </c>
       <c r="H28" s="14">
-        <v>-33.333333333333</v>
+        <v>300</v>
       </c>
       <c r="I28" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J28" s="15">
         <v>4</v>
       </c>
       <c r="K28" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L28" s="14">
-        <v>-60</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="15">
-        <v>1</v>
-      </c>
-      <c r="E29" s="14">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1497,10 +1497,10 @@
         <v>21</v>
       </c>
       <c r="M29" s="14">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N29" s="14">
-        <v>-84.615384615384</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="15">
-        <v>1</v>
-      </c>
-      <c r="E30" s="14">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1538,10 +1538,10 @@
         <v>21</v>
       </c>
       <c r="M30" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="14">
-        <v>-87.5</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1560,11 +1560,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="15">
         <v>1</v>
@@ -1575,8 +1575,8 @@
       <c r="K31" s="14">
         <v>-50</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="14">
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-070pct.xlsx
+++ b/data/source/weekly/cs-en-us-070pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="15">
+        <v>2</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-50</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="15">
+        <v>2</v>
+      </c>
+      <c r="H15" s="14">
+        <v>-50</v>
       </c>
       <c r="I15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15" s="14">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="L15" s="14">
         <v>0</v>
       </c>
-      <c r="L15" s="13" t="s">
-        <v>21</v>
-      </c>
       <c r="M15" s="14">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N15" s="14">
-        <v>-92.307692307692</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D16" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>-83.333333333333</v>
+        <v>150</v>
       </c>
       <c r="F16" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G16" s="15">
         <v>20</v>
       </c>
       <c r="H16" s="14">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="I16" s="15">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J16" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K16" s="14">
-        <v>-41.935483870967</v>
+        <v>-30.303030303030</v>
       </c>
       <c r="L16" s="14">
-        <v>-28</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="M16" s="14">
-        <v>-53.846153846153</v>
+        <v>-47.727272727272</v>
       </c>
       <c r="N16" s="14">
-        <v>-93.478260869565</v>
+        <v>-92.767295597484</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>-61.538461538461</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F17" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G17" s="15">
         <v>30</v>
       </c>
       <c r="H17" s="14">
-        <v>-56.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I17" s="15">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J17" s="15">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="K17" s="14">
-        <v>-40.384615384615</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="L17" s="14">
-        <v>-24.390243902439</v>
+        <v>-20</v>
       </c>
       <c r="M17" s="14">
-        <v>-31.111111111111</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>-68.686868686868</v>
+        <v>-67.272727272727</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
+        <v>300</v>
+      </c>
+      <c r="F18" s="15">
+        <v>9</v>
+      </c>
+      <c r="G18" s="15">
+        <v>8</v>
+      </c>
+      <c r="H18" s="14">
+        <v>12.5</v>
+      </c>
+      <c r="I18" s="15">
+        <v>13</v>
+      </c>
+      <c r="J18" s="15">
+        <v>13</v>
+      </c>
+      <c r="K18" s="14">
         <v>0</v>
       </c>
-      <c r="F18" s="15">
-        <v>6</v>
-      </c>
-      <c r="G18" s="15">
-        <v>9</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="I18" s="15">
-        <v>9</v>
-      </c>
-      <c r="J18" s="15">
-        <v>12</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-25</v>
-      </c>
       <c r="L18" s="14">
-        <v>-30.769230769230</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M18" s="14">
-        <v>-70</v>
+        <v>-62.857142857142</v>
       </c>
       <c r="N18" s="14">
-        <v>-97.931034482758</v>
+        <v>-97.368421052631</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D19" s="15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E19" s="14">
-        <v>333.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G19" s="15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H19" s="14">
-        <v>28.571428571428</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I19" s="15">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J19" s="15">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="K19" s="14">
-        <v>9.090909090909</v>
+        <v>5.555555555555</v>
       </c>
       <c r="L19" s="14">
-        <v>-4</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="M19" s="14">
-        <v>-25</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="N19" s="14">
-        <v>-60.330578512396</v>
+        <v>-58.394160583941</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>300</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G20" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J20" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K20" s="14">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L20" s="14">
-        <v>-41.176470588235</v>
+        <v>-40</v>
       </c>
       <c r="M20" s="14">
-        <v>-61.538461538461</v>
+        <v>-61.290322580645</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.855345911949</v>
+        <v>-96.685082872928</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F21" s="17">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G21" s="17">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H21" s="18">
-        <v>-26.315789473684</v>
+        <v>-17.525773195876</v>
       </c>
       <c r="I21" s="17">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="J21" s="17">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.476510067114</v>
+        <v>-17.341040462427</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.863013698630</v>
+        <v>-16.860465116279</v>
       </c>
       <c r="M21" s="18">
-        <v>-43.478260869565</v>
+        <v>-39.406779661016</v>
       </c>
       <c r="N21" s="18">
-        <v>-90.794649881982</v>
+        <v>-90.110650069156</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>0</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
         <v>2</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D24" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E24" s="14">
-        <v>-9.090909090909</v>
+        <v>-52</v>
       </c>
       <c r="F24" s="15">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G24" s="15">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H24" s="14">
-        <v>-18.390804597701</v>
+        <v>-25.555555555555</v>
       </c>
       <c r="I24" s="15">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="J24" s="15">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="K24" s="14">
-        <v>-21.739130434782</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="L24" s="14">
-        <v>-47.058823529411</v>
+        <v>-54.901960784313</v>
       </c>
       <c r="M24" s="14">
-        <v>-13.698630136986</v>
+        <v>-18.823529411764</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D25" s="15">
         <v>9</v>
       </c>
       <c r="E25" s="14">
-        <v>-22.222222222222</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F25" s="15">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G25" s="15">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H25" s="14">
-        <v>-56.521739130434</v>
+        <v>-41.025641025641</v>
       </c>
       <c r="I25" s="15">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J25" s="15">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="K25" s="14">
-        <v>-66.666666666666</v>
+        <v>-64.761904761904</v>
       </c>
       <c r="L25" s="14">
-        <v>-77.777777777777</v>
+        <v>-80.319148936170</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>12</v>
+      </c>
+      <c r="D26" s="15">
         <v>8</v>
       </c>
-      <c r="D26" s="15">
-        <v>10</v>
-      </c>
       <c r="E26" s="14">
-        <v>-20</v>
+        <v>50</v>
       </c>
       <c r="F26" s="15">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G26" s="15">
         <v>37</v>
       </c>
       <c r="H26" s="14">
-        <v>8.108108108108</v>
+        <v>16.216216216216</v>
       </c>
       <c r="I26" s="15">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J26" s="15">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="K26" s="14">
-        <v>23.809523809523</v>
+        <v>26.760563380281</v>
       </c>
       <c r="L26" s="14">
-        <v>5.405405405405</v>
+        <v>3.448275862068</v>
       </c>
       <c r="M26" s="14">
-        <v>-20.408163265306</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="15">
+        <v>2</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-50</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="15">
+        <v>2</v>
+      </c>
+      <c r="H27" s="14">
+        <v>-50</v>
       </c>
       <c r="I27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K27" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L27" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>5</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>400</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G28" s="15">
         <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="I28" s="15">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K28" s="14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L28" s="14">
-        <v>-33.333333333333</v>
+        <v>12.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="N29" s="14">
-        <v>-88.888888888888</v>
+        <v>-89.473684210526</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N30" s="14">
-        <v>-91.666666666666</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1576,7 +1576,7 @@
         <v>-50</v>
       </c>
       <c r="L31" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-070pct.xlsx
+++ b/data/source/weekly/cs-en-us-070pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,14 +892,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
-      </c>
-      <c r="D15" s="15">
-        <v>2</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-50</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
@@ -926,48 +926,48 @@
         <v>-33.333333333333</v>
       </c>
       <c r="N15" s="14">
-        <v>-87.5</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>5</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>150</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G16" s="15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H16" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I16" s="15">
         <v>23</v>
       </c>
       <c r="J16" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K16" s="14">
-        <v>-30.303030303030</v>
+        <v>-36.111111111111</v>
       </c>
       <c r="L16" s="14">
-        <v>-17.857142857142</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="M16" s="14">
-        <v>-47.727272727272</v>
+        <v>-56.603773584905</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.767295597484</v>
+        <v>-93.628808864265</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,78 +978,78 @@
         <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E17" s="14">
-        <v>-16.666666666666</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G17" s="15">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H17" s="14">
-        <v>-50</v>
+        <v>-55.263157894736</v>
       </c>
       <c r="I17" s="15">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J17" s="15">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="K17" s="14">
-        <v>-37.931034482758</v>
+        <v>-41.428571428571</v>
       </c>
       <c r="L17" s="14">
-        <v>-20</v>
+        <v>-19.607843137254</v>
       </c>
       <c r="M17" s="14">
-        <v>-33.333333333333</v>
+        <v>-36.923076923076</v>
       </c>
       <c r="N17" s="14">
-        <v>-67.272727272727</v>
+        <v>-67.96875</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>4</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
         <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H18" s="14">
-        <v>12.5</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I18" s="15">
         <v>13</v>
       </c>
       <c r="J18" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" s="14">
-        <v>0</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L18" s="14">
-        <v>-7.142857142857</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="M18" s="14">
-        <v>-62.857142857142</v>
+        <v>-63.888888888888</v>
       </c>
       <c r="N18" s="14">
-        <v>-97.368421052631</v>
+        <v>-97.670250896057</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>10</v>
       </c>
       <c r="D19" s="15">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E19" s="14">
-        <v>0</v>
+        <v>-37.5</v>
       </c>
       <c r="F19" s="15">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G19" s="15">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H19" s="14">
-        <v>33.333333333333</v>
+        <v>10.810810810810</v>
       </c>
       <c r="I19" s="15">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="J19" s="15">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="K19" s="14">
-        <v>5.555555555555</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L19" s="14">
-        <v>-9.523809523809</v>
+        <v>-10.958904109589</v>
       </c>
       <c r="M19" s="14">
-        <v>-17.391304347826</v>
+        <v>-20.731707317073</v>
       </c>
       <c r="N19" s="14">
-        <v>-58.394160583941</v>
+        <v>-60.122699386503</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,13 +1098,13 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F20" s="15">
         <v>7</v>
@@ -1116,22 +1116,22 @@
         <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J20" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K20" s="14">
         <v>0</v>
       </c>
       <c r="L20" s="14">
-        <v>-40</v>
+        <v>-35</v>
       </c>
       <c r="M20" s="14">
-        <v>-61.290322580645</v>
+        <v>-58.064516129032</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.685082872928</v>
+        <v>-96.758104738154</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E21" s="18">
-        <v>12.5</v>
+        <v>-51.515151515151</v>
       </c>
       <c r="F21" s="17">
         <v>80</v>
       </c>
       <c r="G21" s="17">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="H21" s="18">
-        <v>-17.525773195876</v>
+        <v>-26.605504587156</v>
       </c>
       <c r="I21" s="17">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="J21" s="17">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.341040462427</v>
+        <v>-23.786407766990</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.860465116279</v>
+        <v>-19.487179487179</v>
       </c>
       <c r="M21" s="18">
-        <v>-39.406779661016</v>
+        <v>-41.851851851851</v>
       </c>
       <c r="N21" s="18">
-        <v>-90.110650069156</v>
+        <v>-90.426829268292</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,25 +1189,25 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I22" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="15">
         <v>1</v>
       </c>
       <c r="K22" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L22" s="14">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M22" s="14">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D24" s="15">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="E24" s="14">
-        <v>-52</v>
+        <v>-56.521739130434</v>
       </c>
       <c r="F24" s="15">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="G24" s="15">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="H24" s="14">
-        <v>-25.555555555555</v>
+        <v>-31.858407079646</v>
       </c>
       <c r="I24" s="15">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="J24" s="15">
-        <v>186</v>
+        <v>232</v>
       </c>
       <c r="K24" s="14">
-        <v>-25.806451612903</v>
+        <v>-31.465517241379</v>
       </c>
       <c r="L24" s="14">
-        <v>-54.901960784313</v>
+        <v>-54.571428571428</v>
       </c>
       <c r="M24" s="14">
-        <v>-18.823529411764</v>
+        <v>-13.114754098360</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" s="15">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E25" s="14">
-        <v>-44.444444444444</v>
+        <v>-84.210526315789</v>
       </c>
       <c r="F25" s="15">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G25" s="15">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H25" s="14">
-        <v>-41.025641025641</v>
+        <v>-58.695652173913</v>
       </c>
       <c r="I25" s="15">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J25" s="15">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="K25" s="14">
-        <v>-64.761904761904</v>
+        <v>-67.741935483871</v>
       </c>
       <c r="L25" s="14">
-        <v>-80.319148936170</v>
+        <v>-80.861244019138</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E26" s="14">
-        <v>50</v>
+        <v>-60</v>
       </c>
       <c r="F26" s="15">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G26" s="15">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H26" s="14">
-        <v>16.216216216216</v>
+        <v>-15.909090909090</v>
       </c>
       <c r="I26" s="15">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="J26" s="15">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="K26" s="14">
-        <v>26.760563380281</v>
+        <v>11.627906976744</v>
       </c>
       <c r="L26" s="14">
-        <v>3.448275862068</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="M26" s="14">
-        <v>-18.918918918918</v>
+        <v>-19.327731092437</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15">
-        <v>2</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-50</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
@@ -1426,22 +1426,22 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>5</v>
-      </c>
-      <c r="D28" s="15">
         <v>1</v>
       </c>
-      <c r="E28" s="14">
-        <v>400</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G28" s="15">
         <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="I28" s="15">
         <v>9</v>
@@ -1453,7 +1453,7 @@
         <v>80</v>
       </c>
       <c r="L28" s="14">
-        <v>12.5</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>-100</v>
       </c>
       <c r="I31" s="15">
         <v>1</v>
       </c>
       <c r="J31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L31" s="14">
         <v>-50</v>

--- a/data/source/weekly/cs-en-us-070pct.xlsx
+++ b/data/source/weekly/cs-en-us-070pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -923,51 +923,51 @@
         <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N15" s="14">
-        <v>-90</v>
+        <v>-90.476190476190</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>1</v>
       </c>
       <c r="D16" s="15">
         <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="15">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H16" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J16" s="15">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K16" s="14">
-        <v>-36.111111111111</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="L16" s="14">
-        <v>-25.806451612903</v>
+        <v>-25</v>
       </c>
       <c r="M16" s="14">
-        <v>-56.603773584905</v>
+        <v>-59.322033898305</v>
       </c>
       <c r="N16" s="14">
-        <v>-93.628808864265</v>
+        <v>-94.029850746268</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E17" s="14">
-        <v>-58.333333333333</v>
+        <v>-87.5</v>
       </c>
       <c r="F17" s="15">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G17" s="15">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H17" s="14">
-        <v>-55.263157894736</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="I17" s="15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J17" s="15">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="K17" s="14">
-        <v>-41.428571428571</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L17" s="14">
-        <v>-19.607843137254</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M17" s="14">
-        <v>-36.923076923076</v>
+        <v>-40.845070422535</v>
       </c>
       <c r="N17" s="14">
-        <v>-67.96875</v>
+        <v>-70.422535211267</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="15">
         <v>8</v>
       </c>
       <c r="G18" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H18" s="14">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="I18" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K18" s="14">
-        <v>-7.142857142857</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="L18" s="14">
-        <v>-27.777777777777</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M18" s="14">
-        <v>-63.888888888888</v>
+        <v>-65.853658536585</v>
       </c>
       <c r="N18" s="14">
-        <v>-97.670250896057</v>
+        <v>-97.723577235772</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="15">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G19" s="15">
         <v>37</v>
       </c>
       <c r="H19" s="14">
-        <v>10.810810810810</v>
+        <v>0</v>
       </c>
       <c r="I19" s="15">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J19" s="15">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="K19" s="14">
-        <v>-7.142857142857</v>
+        <v>-8.974358974358</v>
       </c>
       <c r="L19" s="14">
-        <v>-10.958904109589</v>
+        <v>-15.476190476190</v>
       </c>
       <c r="M19" s="14">
-        <v>-20.731707317073</v>
+        <v>-21.111111111111</v>
       </c>
       <c r="N19" s="14">
-        <v>-60.122699386503</v>
+        <v>-60.112359550561</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I20" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J20" s="15">
         <v>13</v>
       </c>
       <c r="K20" s="14">
-        <v>0</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L20" s="14">
-        <v>-35</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M20" s="14">
-        <v>-58.064516129032</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.758104738154</v>
+        <v>-96.868008948545</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D21" s="17">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-51.515151515151</v>
+        <v>-50</v>
       </c>
       <c r="F21" s="17">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G21" s="17">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H21" s="18">
-        <v>-26.605504587156</v>
+        <v>-27.619047619047</v>
       </c>
       <c r="I21" s="17">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="J21" s="17">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="K21" s="18">
-        <v>-23.786407766990</v>
+        <v>-26.754385964912</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.487179487179</v>
+        <v>-22.325581395348</v>
       </c>
       <c r="M21" s="18">
-        <v>-41.851851851851</v>
+        <v>-44.884488448844</v>
       </c>
       <c r="N21" s="18">
-        <v>-90.426829268292</v>
+        <v>-90.793825799338</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1198,19 +1198,19 @@
         <v>200</v>
       </c>
       <c r="I22" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="15">
         <v>1</v>
       </c>
       <c r="K22" s="14">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="L22" s="14">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D24" s="15">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="E24" s="14">
-        <v>-56.521739130434</v>
+        <v>-16</v>
       </c>
       <c r="F24" s="15">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G24" s="15">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H24" s="14">
-        <v>-31.858407079646</v>
+        <v>-38.135593220339</v>
       </c>
       <c r="I24" s="15">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="J24" s="15">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="K24" s="14">
-        <v>-31.465517241379</v>
+        <v>-29.961089494163</v>
       </c>
       <c r="L24" s="14">
-        <v>-54.571428571428</v>
+        <v>-52.755905511811</v>
       </c>
       <c r="M24" s="14">
-        <v>-13.114754098360</v>
+        <v>-13.875598086124</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D25" s="15">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E25" s="14">
-        <v>-84.210526315789</v>
+        <v>-43.75</v>
       </c>
       <c r="F25" s="15">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G25" s="15">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H25" s="14">
-        <v>-58.695652173913</v>
+        <v>-54.716981132075</v>
       </c>
       <c r="I25" s="15">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J25" s="15">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="K25" s="14">
-        <v>-67.741935483871</v>
+        <v>-65</v>
       </c>
       <c r="L25" s="14">
-        <v>-80.861244019138</v>
+        <v>-78.026905829596</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D26" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E26" s="14">
-        <v>-60</v>
+        <v>71.428571428571</v>
       </c>
       <c r="F26" s="15">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G26" s="15">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H26" s="14">
-        <v>-15.909090909090</v>
+        <v>6.382978723404</v>
       </c>
       <c r="I26" s="15">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="J26" s="15">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="K26" s="14">
-        <v>11.627906976744</v>
+        <v>20</v>
       </c>
       <c r="L26" s="14">
-        <v>-3.030303030303</v>
+        <v>6.194690265486</v>
       </c>
       <c r="M26" s="14">
-        <v>-19.327731092437</v>
+        <v>-6.25</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
         <v>8</v>
       </c>
       <c r="G28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="I28" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>80</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L28" s="14">
-        <v>-30.769230769230</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="15">
-        <v>1</v>
-      </c>
-      <c r="H29" s="14">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="15">
         <v>2</v>
@@ -1500,7 +1500,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="N29" s="14">
-        <v>-89.473684210526</v>
+        <v>-90.476190476190</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="15">
-        <v>1</v>
-      </c>
-      <c r="H30" s="14">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="15">
         <v>1</v>
@@ -1541,7 +1541,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N30" s="14">
-        <v>-92.307692307692</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1561,7 +1561,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>
@@ -1570,10 +1570,10 @@
         <v>1</v>
       </c>
       <c r="J31" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L31" s="14">
         <v>-50</v>
@@ -1634,8 +1634,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="14">
+        <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-070pct.xlsx
+++ b/data/source/weekly/cs-en-us-070pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,38 +895,38 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
       </c>
       <c r="J15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="N15" s="14">
-        <v>-90.476190476190</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -946,28 +946,28 @@
         <v>7</v>
       </c>
       <c r="G16" s="15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H16" s="14">
-        <v>-50</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I16" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J16" s="15">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K16" s="14">
-        <v>-38.461538461538</v>
+        <v>-40.476190476190</v>
       </c>
       <c r="L16" s="14">
-        <v>-25</v>
+        <v>-30.555555555555</v>
       </c>
       <c r="M16" s="14">
-        <v>-59.322033898305</v>
+        <v>-65.277777777777</v>
       </c>
       <c r="N16" s="14">
-        <v>-94.029850746268</v>
+        <v>-94.266055045871</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" s="14">
-        <v>-87.5</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F17" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17" s="15">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H17" s="14">
-        <v>-61.538461538461</v>
+        <v>-54.285714285714</v>
       </c>
       <c r="I17" s="15">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J17" s="15">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K17" s="14">
-        <v>-46.153846153846</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="L17" s="14">
-        <v>-22.222222222222</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M17" s="14">
-        <v>-40.845070422535</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="N17" s="14">
-        <v>-70.422535211267</v>
+        <v>-69.230769230769</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>-66.666666666666</v>
       </c>
       <c r="F18" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G18" s="15">
         <v>8</v>
       </c>
       <c r="H18" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I18" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K18" s="14">
-        <v>-17.647058823529</v>
+        <v>-25</v>
       </c>
       <c r="L18" s="14">
-        <v>-36.363636363636</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="M18" s="14">
-        <v>-65.853658536585</v>
+        <v>-67.391304347826</v>
       </c>
       <c r="N18" s="14">
-        <v>-97.723577235772</v>
+        <v>-97.740963855421</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D19" s="15">
         <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>-25</v>
+        <v>62.5</v>
       </c>
       <c r="F19" s="15">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G19" s="15">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H19" s="14">
-        <v>0</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I19" s="15">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="J19" s="15">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="K19" s="14">
-        <v>-8.974358974358</v>
+        <v>-2.325581395348</v>
       </c>
       <c r="L19" s="14">
-        <v>-15.476190476190</v>
+        <v>-13.402061855670</v>
       </c>
       <c r="M19" s="14">
-        <v>-21.111111111111</v>
+        <v>-18.446601941747</v>
       </c>
       <c r="N19" s="14">
-        <v>-60.112359550561</v>
+        <v>-57.360406091370</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
+        <v>3</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G20" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>60</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I20" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J20" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K20" s="14">
-        <v>7.692307692307</v>
+        <v>-6.25</v>
       </c>
       <c r="L20" s="14">
-        <v>-33.333333333333</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="M20" s="14">
-        <v>-63.157894736842</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.868008948545</v>
+        <v>-96.801705756929</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>-50</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F21" s="17">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G21" s="17">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H21" s="18">
-        <v>-27.619047619047</v>
+        <v>-30.188679245283</v>
       </c>
       <c r="I21" s="17">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="J21" s="17">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="K21" s="18">
-        <v>-26.754385964912</v>
+        <v>-25.882352941176</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.325581395348</v>
+        <v>-19.915254237288</v>
       </c>
       <c r="M21" s="18">
-        <v>-44.884488448844</v>
+        <v>-45.058139534883</v>
       </c>
       <c r="N21" s="18">
-        <v>-90.793825799338</v>
+        <v>-90.322580645161</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>3</v>
-      </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14">
-        <v>200</v>
+        <v>2</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="15">
         <v>6</v>
@@ -1207,10 +1207,10 @@
         <v>500</v>
       </c>
       <c r="L22" s="14">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="M22" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D24" s="15">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E24" s="14">
-        <v>-16</v>
+        <v>-43.589743589743</v>
       </c>
       <c r="F24" s="15">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G24" s="15">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="H24" s="14">
-        <v>-38.135593220339</v>
+        <v>-43.703703703703</v>
       </c>
       <c r="I24" s="15">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="J24" s="15">
-        <v>257</v>
+        <v>296</v>
       </c>
       <c r="K24" s="14">
-        <v>-29.961089494163</v>
+        <v>-31.418918918918</v>
       </c>
       <c r="L24" s="14">
-        <v>-52.755905511811</v>
+        <v>-50.728155339805</v>
       </c>
       <c r="M24" s="14">
-        <v>-13.875598086124</v>
+        <v>-13.983050847457</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E25" s="14">
-        <v>-43.75</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="F25" s="15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G25" s="15">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H25" s="14">
-        <v>-54.716981132075</v>
+        <v>-65.151515151515</v>
       </c>
       <c r="I25" s="15">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J25" s="15">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="K25" s="14">
-        <v>-65</v>
+        <v>-66.049382716049</v>
       </c>
       <c r="L25" s="14">
-        <v>-78.026905829596</v>
+        <v>-77.178423236514</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D26" s="15">
         <v>14</v>
       </c>
       <c r="E26" s="14">
-        <v>71.428571428571</v>
+        <v>21.428571428571</v>
       </c>
       <c r="F26" s="15">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G26" s="15">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H26" s="14">
-        <v>6.382978723404</v>
+        <v>15.686274509803</v>
       </c>
       <c r="I26" s="15">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="J26" s="15">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="K26" s="14">
-        <v>20</v>
+        <v>20.175438596491</v>
       </c>
       <c r="L26" s="14">
-        <v>6.194690265486</v>
+        <v>5.384615384615</v>
       </c>
       <c r="M26" s="14">
-        <v>-6.25</v>
+        <v>-8.053691275167</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>2</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I27" s="15">
         <v>2</v>
       </c>
       <c r="J27" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K27" s="14">
-        <v>-33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="L27" s="14">
         <v>-66.666666666666</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
         <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I28" s="15">
         <v>10</v>
       </c>
       <c r="J28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K28" s="14">
-        <v>66.666666666666</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L28" s="14">
-        <v>-28.571428571428</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>-75</v>
       </c>
       <c r="L31" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-070pct.xlsx
+++ b/data/source/weekly/cs-en-us-070pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -881,8 +881,8 @@
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="14">
+        <v>-100</v>
       </c>
       <c r="N14" s="14">
         <v>-100</v>
@@ -901,23 +901,23 @@
       <c r="E15" s="14">
         <v>-100</v>
       </c>
-      <c r="F15" s="15">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
       </c>
       <c r="J15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
@@ -937,37 +937,37 @@
         <v>1</v>
       </c>
       <c r="D16" s="15">
+        <v>2</v>
+      </c>
+      <c r="E16" s="14">
+        <v>-50</v>
+      </c>
+      <c r="F16" s="15">
         <v>3</v>
-      </c>
-      <c r="E16" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F16" s="15">
-        <v>7</v>
       </c>
       <c r="G16" s="15">
         <v>11</v>
       </c>
       <c r="H16" s="14">
-        <v>-36.363636363636</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="I16" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J16" s="15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K16" s="14">
-        <v>-40.476190476190</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="L16" s="14">
-        <v>-30.555555555555</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="M16" s="14">
-        <v>-65.277777777777</v>
+        <v>-67.5</v>
       </c>
       <c r="N16" s="14">
-        <v>-94.266055045871</v>
+        <v>-94.594594594594</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" s="14">
-        <v>-44.444444444444</v>
+        <v>-40</v>
       </c>
       <c r="F17" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G17" s="15">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H17" s="14">
-        <v>-54.285714285714</v>
+        <v>-56.410256410256</v>
       </c>
       <c r="I17" s="15">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J17" s="15">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="K17" s="14">
-        <v>-44.827586206896</v>
+        <v>-44.329896907216</v>
       </c>
       <c r="L17" s="14">
-        <v>-14.285714285714</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="M17" s="14">
-        <v>-36.842105263157</v>
+        <v>-34.939759036144</v>
       </c>
       <c r="N17" s="14">
-        <v>-69.230769230769</v>
+        <v>-69.142857142857</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G18" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H18" s="14">
-        <v>-25</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I18" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J18" s="15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K18" s="14">
-        <v>-25</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="L18" s="14">
-        <v>-34.782608695652</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="M18" s="14">
-        <v>-67.391304347826</v>
+        <v>-66</v>
       </c>
       <c r="N18" s="14">
-        <v>-97.740963855421</v>
+        <v>-97.585227272727</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D19" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19" s="14">
-        <v>62.5</v>
+        <v>-30</v>
       </c>
       <c r="F19" s="15">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G19" s="15">
         <v>42</v>
       </c>
       <c r="H19" s="14">
-        <v>-7.142857142857</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I19" s="15">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="J19" s="15">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="K19" s="14">
-        <v>-2.325581395348</v>
+        <v>-5.208333333333</v>
       </c>
       <c r="L19" s="14">
-        <v>-13.402061855670</v>
+        <v>-14.953271028037</v>
       </c>
       <c r="M19" s="14">
-        <v>-18.446601941747</v>
+        <v>-20.175438596491</v>
       </c>
       <c r="N19" s="14">
-        <v>-57.360406091370</v>
+        <v>-57.476635514018</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>2</v>
+      </c>
+      <c r="D20" s="15">
         <v>1</v>
       </c>
-      <c r="D20" s="15">
-        <v>3</v>
-      </c>
       <c r="E20" s="14">
-        <v>-66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F20" s="15">
+        <v>6</v>
+      </c>
+      <c r="G20" s="15">
         <v>5</v>
       </c>
-      <c r="G20" s="15">
-        <v>7</v>
-      </c>
       <c r="H20" s="14">
-        <v>-28.571428571428</v>
+        <v>20</v>
       </c>
       <c r="I20" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J20" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K20" s="14">
-        <v>-6.25</v>
+        <v>0</v>
       </c>
       <c r="L20" s="14">
-        <v>-31.818181818181</v>
+        <v>-32</v>
       </c>
       <c r="M20" s="14">
-        <v>-64.285714285714</v>
+        <v>-64.583333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.801705756929</v>
+        <v>-96.673189823874</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>-22.222222222222</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="F21" s="17">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G21" s="17">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H21" s="18">
-        <v>-30.188679245283</v>
+        <v>-40</v>
       </c>
       <c r="I21" s="17">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="J21" s="17">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="K21" s="18">
-        <v>-25.882352941176</v>
+        <v>-26.855123674911</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.915254237288</v>
+        <v>-19.455252918287</v>
       </c>
       <c r="M21" s="18">
-        <v>-45.058139534883</v>
+        <v>-45.669291338582</v>
       </c>
       <c r="N21" s="18">
-        <v>-90.322580645161</v>
+        <v>-90.217391304347</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1207,10 +1207,10 @@
         <v>500</v>
       </c>
       <c r="L22" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D24" s="15">
         <v>39</v>
       </c>
       <c r="E24" s="14">
-        <v>-43.589743589743</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F24" s="15">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G24" s="15">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="H24" s="14">
-        <v>-43.703703703703</v>
+        <v>-42.281879194630</v>
       </c>
       <c r="I24" s="15">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="J24" s="15">
-        <v>296</v>
+        <v>335</v>
       </c>
       <c r="K24" s="14">
-        <v>-31.418918918918</v>
+        <v>-32.835820895522</v>
       </c>
       <c r="L24" s="14">
-        <v>-50.728155339805</v>
+        <v>-50</v>
       </c>
       <c r="M24" s="14">
-        <v>-13.983050847457</v>
+        <v>-11.067193675889</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D25" s="15">
         <v>22</v>
       </c>
       <c r="E25" s="14">
-        <v>-72.727272727272</v>
+        <v>-59.090909090909</v>
       </c>
       <c r="F25" s="15">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G25" s="15">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="H25" s="14">
-        <v>-65.151515151515</v>
+        <v>-64.556962025316</v>
       </c>
       <c r="I25" s="15">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J25" s="15">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="K25" s="14">
-        <v>-66.049382716049</v>
+        <v>-64.673913043478</v>
       </c>
       <c r="L25" s="14">
-        <v>-77.178423236514</v>
+        <v>-75.655430711610</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D26" s="15">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14">
-        <v>21.428571428571</v>
+        <v>30</v>
       </c>
       <c r="F26" s="15">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G26" s="15">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H26" s="14">
-        <v>15.686274509803</v>
+        <v>15.094339622641</v>
       </c>
       <c r="I26" s="15">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="J26" s="15">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K26" s="14">
-        <v>20.175438596491</v>
+        <v>21.774193548387</v>
       </c>
       <c r="L26" s="14">
-        <v>5.384615384615</v>
+        <v>-0.657894736842</v>
       </c>
       <c r="M26" s="14">
-        <v>-8.053691275167</v>
+        <v>-8.484848484848</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,28 +1388,28 @@
         <v>20</v>
       </c>
       <c r="D27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="14">
         <v>-100</v>
       </c>
-      <c r="F27" s="15">
-        <v>1</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="15">
         <v>2</v>
       </c>
       <c r="J27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L27" s="14">
         <v>-66.666666666666</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>1</v>
       </c>
       <c r="D28" s="15">
         <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
         <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="14">
-        <v>42.857142857142</v>
+        <v>37.5</v>
       </c>
       <c r="L28" s="14">
-        <v>-33.333333333333</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="15">
+        <v>1</v>
+      </c>
+      <c r="E29" s="14">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="15">
+        <v>1</v>
+      </c>
+      <c r="H29" s="14">
+        <v>-100</v>
       </c>
       <c r="I29" s="15">
         <v>2</v>
       </c>
       <c r="J29" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M29" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N29" s="14">
-        <v>-90.476190476190</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="15">
+        <v>1</v>
+      </c>
+      <c r="E30" s="14">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="15">
+        <v>1</v>
+      </c>
+      <c r="H30" s="14">
+        <v>-100</v>
       </c>
       <c r="I30" s="15">
         <v>1</v>
       </c>
       <c r="J30" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M30" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="14">
-        <v>-93.333333333333</v>
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-070pct.xlsx
+++ b/data/source/weekly/cs-en-us-070pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -920,27 +920,27 @@
         <v>-60</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M15" s="14">
         <v>-60</v>
       </c>
       <c r="N15" s="14">
-        <v>-90.909090909090</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
         <v>3</v>
@@ -955,19 +955,19 @@
         <v>26</v>
       </c>
       <c r="J16" s="15">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K16" s="14">
-        <v>-40.909090909090</v>
+        <v>-44.680851063829</v>
       </c>
       <c r="L16" s="14">
-        <v>-31.578947368421</v>
+        <v>-36.585365853658</v>
       </c>
       <c r="M16" s="14">
-        <v>-67.5</v>
+        <v>-72.916666666666</v>
       </c>
       <c r="N16" s="14">
-        <v>-94.594594594594</v>
+        <v>-95.131086142322</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E17" s="14">
-        <v>-40</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G17" s="15">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H17" s="14">
-        <v>-56.410256410256</v>
+        <v>-60</v>
       </c>
       <c r="I17" s="15">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J17" s="15">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="K17" s="14">
-        <v>-44.329896907216</v>
+        <v>-48.695652173913</v>
       </c>
       <c r="L17" s="14">
-        <v>-6.896551724137</v>
+        <v>-4.838709677419</v>
       </c>
       <c r="M17" s="14">
-        <v>-34.939759036144</v>
+        <v>-35.164835164835</v>
       </c>
       <c r="N17" s="14">
-        <v>-69.142857142857</v>
+        <v>-69.109947643979</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E18" s="14">
-        <v>-50</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="F18" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G18" s="15">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H18" s="14">
-        <v>-63.636363636363</v>
+        <v>-69.565217391304</v>
       </c>
       <c r="I18" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J18" s="15">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="K18" s="14">
-        <v>-29.166666666666</v>
+        <v>-45.945945945945</v>
       </c>
       <c r="L18" s="14">
-        <v>-37.037037037037</v>
+        <v>-37.5</v>
       </c>
       <c r="M18" s="14">
-        <v>-66</v>
+        <v>-65.517241379310</v>
       </c>
       <c r="N18" s="14">
-        <v>-97.585227272727</v>
+        <v>-97.336884154460</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>9</v>
+      </c>
+      <c r="D19" s="15">
         <v>7</v>
       </c>
-      <c r="D19" s="15">
-        <v>10</v>
-      </c>
       <c r="E19" s="14">
-        <v>-30</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F19" s="15">
         <v>36</v>
       </c>
       <c r="G19" s="15">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H19" s="14">
-        <v>-14.285714285714</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I19" s="15">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="J19" s="15">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="K19" s="14">
-        <v>-5.208333333333</v>
+        <v>-0.970873786407</v>
       </c>
       <c r="L19" s="14">
-        <v>-14.953271028037</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="M19" s="14">
-        <v>-20.175438596491</v>
+        <v>-20.930232558139</v>
       </c>
       <c r="N19" s="14">
-        <v>-57.476635514018</v>
+        <v>-56.595744680851</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E20" s="14">
-        <v>100</v>
+        <v>-62.5</v>
       </c>
       <c r="F20" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H20" s="14">
-        <v>20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J20" s="15">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="K20" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L20" s="14">
-        <v>-32</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M20" s="14">
-        <v>-64.583333333333</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.673189823874</v>
+        <v>-96.389891696750</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,45 +1142,45 @@
         <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E21" s="18">
-        <v>-35.714285714285</v>
+        <v>-63.265306122449</v>
       </c>
       <c r="F21" s="17">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G21" s="17">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="H21" s="18">
-        <v>-40</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I21" s="17">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="J21" s="17">
-        <v>283</v>
+        <v>332</v>
       </c>
       <c r="K21" s="18">
-        <v>-26.855123674911</v>
+        <v>-31.024096385542</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.455252918287</v>
+        <v>-18.214285714285</v>
       </c>
       <c r="M21" s="18">
-        <v>-45.669291338582</v>
+        <v>-47.477064220183</v>
       </c>
       <c r="N21" s="18">
-        <v>-90.217391304347</v>
+        <v>-90.043478260869</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="15">
         <v>1</v>
       </c>
       <c r="K22" s="14">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="L22" s="14">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M22" s="14">
-        <v>-33.333333333333</v>
+        <v>-30</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D24" s="15">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E24" s="14">
-        <v>-46.153846153846</v>
+        <v>21.875</v>
       </c>
       <c r="F24" s="15">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="G24" s="15">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="H24" s="14">
-        <v>-42.281879194630</v>
+        <v>-22.962962962963</v>
       </c>
       <c r="I24" s="15">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="J24" s="15">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="K24" s="14">
-        <v>-32.835820895522</v>
+        <v>-28.610354223433</v>
       </c>
       <c r="L24" s="14">
-        <v>-50</v>
+        <v>-44.957983193277</v>
       </c>
       <c r="M24" s="14">
-        <v>-11.067193675889</v>
+        <v>-7.420494699646</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E25" s="14">
-        <v>-59.090909090909</v>
+        <v>-62.5</v>
       </c>
       <c r="F25" s="15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G25" s="15">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H25" s="14">
-        <v>-64.556962025316</v>
+        <v>-60.526315789473</v>
       </c>
       <c r="I25" s="15">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J25" s="15">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="K25" s="14">
-        <v>-64.673913043478</v>
+        <v>-65</v>
       </c>
       <c r="L25" s="14">
-        <v>-75.655430711610</v>
+        <v>-75.524475524475</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D26" s="15">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E26" s="14">
-        <v>30</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="F26" s="15">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="G26" s="15">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="H26" s="14">
-        <v>15.094339622641</v>
+        <v>20.338983050847</v>
       </c>
       <c r="I26" s="15">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="J26" s="15">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="K26" s="14">
-        <v>21.774193548387</v>
+        <v>15.172413793103</v>
       </c>
       <c r="L26" s="14">
-        <v>-0.657894736842</v>
+        <v>3.726708074534</v>
       </c>
       <c r="M26" s="14">
-        <v>-8.484848484848</v>
+        <v>-8.743169398907</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,7 +1397,7 @@
         <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1406,13 +1406,13 @@
         <v>2</v>
       </c>
       <c r="J27" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="14">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="L27" s="14">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="15">
         <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I28" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J28" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="14">
-        <v>37.5</v>
+        <v>55.555555555555</v>
       </c>
       <c r="L28" s="14">
-        <v>-42.105263157894</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="15">
-        <v>1</v>
-      </c>
-      <c r="E29" s="14">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1497,10 +1497,10 @@
         <v>21</v>
       </c>
       <c r="M29" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="14">
-        <v>-91.666666666666</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="15">
-        <v>1</v>
-      </c>
-      <c r="E30" s="14">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1538,10 +1538,10 @@
         <v>21</v>
       </c>
       <c r="M30" s="14">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N30" s="14">
-        <v>-94.444444444444</v>
+        <v>-95.454545454545</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1561,7 +1561,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-070pct.xlsx
+++ b/data/source/weekly/cs-en-us-070pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -895,17 +895,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>2</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" s="14">
         <v>-100</v>
@@ -914,60 +914,60 @@
         <v>2</v>
       </c>
       <c r="J15" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K15" s="14">
-        <v>-60</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="L15" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M15" s="14">
         <v>-60</v>
       </c>
       <c r="N15" s="14">
-        <v>-92.307692307692</v>
+        <v>-93.939393939393</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>2</v>
       </c>
       <c r="D16" s="15">
         <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
         <v>11</v>
       </c>
       <c r="H16" s="14">
-        <v>-72.727272727272</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I16" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J16" s="15">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K16" s="14">
-        <v>-44.680851063829</v>
+        <v>-44</v>
       </c>
       <c r="L16" s="14">
-        <v>-36.585365853658</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M16" s="14">
-        <v>-72.916666666666</v>
+        <v>-72.815533980582</v>
       </c>
       <c r="N16" s="14">
-        <v>-95.131086142322</v>
+        <v>-95.087719298245</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E17" s="14">
-        <v>-83.333333333333</v>
+        <v>-62.5</v>
       </c>
       <c r="F17" s="15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G17" s="15">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="H17" s="14">
-        <v>-60</v>
+        <v>-58.490566037735</v>
       </c>
       <c r="I17" s="15">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J17" s="15">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="K17" s="14">
-        <v>-48.695652173913</v>
+        <v>-50.381679389313</v>
       </c>
       <c r="L17" s="14">
-        <v>-4.838709677419</v>
+        <v>0</v>
       </c>
       <c r="M17" s="14">
-        <v>-35.164835164835</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="N17" s="14">
-        <v>-69.109947643979</v>
+        <v>-68.446601941747</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>-76.923076923076</v>
+        <v>100</v>
       </c>
       <c r="F18" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18" s="15">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H18" s="14">
-        <v>-69.565217391304</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="I18" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J18" s="15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K18" s="14">
-        <v>-45.945945945945</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="L18" s="14">
-        <v>-37.5</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="M18" s="14">
-        <v>-65.517241379310</v>
+        <v>-63.333333333333</v>
       </c>
       <c r="N18" s="14">
-        <v>-97.336884154460</v>
+        <v>-97.260273972602</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E19" s="14">
-        <v>28.571428571428</v>
+        <v>20</v>
       </c>
       <c r="F19" s="15">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G19" s="15">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H19" s="14">
-        <v>9.090909090909</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I19" s="15">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J19" s="15">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="K19" s="14">
-        <v>-0.970873786407</v>
+        <v>-0.884955752212</v>
       </c>
       <c r="L19" s="14">
-        <v>-10.526315789473</v>
+        <v>-10.4</v>
       </c>
       <c r="M19" s="14">
-        <v>-20.930232558139</v>
+        <v>-20.567375886524</v>
       </c>
       <c r="N19" s="14">
-        <v>-56.595744680851</v>
+        <v>-57.575757575757</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>3</v>
       </c>
       <c r="D20" s="15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E20" s="14">
-        <v>-62.5</v>
+        <v>-25</v>
       </c>
       <c r="F20" s="15">
         <v>8</v>
       </c>
       <c r="G20" s="15">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H20" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J20" s="15">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K20" s="14">
-        <v>-20</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="L20" s="14">
-        <v>-28.571428571428</v>
+        <v>-31.25</v>
       </c>
       <c r="M20" s="14">
-        <v>-63.636363636363</v>
+        <v>-61.403508771929</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.389891696750</v>
+        <v>-96.239316239316</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,72 +1139,72 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E21" s="18">
-        <v>-63.265306122449</v>
+        <v>-30.555555555555</v>
       </c>
       <c r="F21" s="17">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="G21" s="17">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="H21" s="18">
-        <v>-42.857142857142</v>
+        <v>-41.428571428571</v>
       </c>
       <c r="I21" s="17">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="J21" s="17">
-        <v>332</v>
+        <v>368</v>
       </c>
       <c r="K21" s="18">
-        <v>-31.024096385542</v>
+        <v>-31.793478260869</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.214285714285</v>
+        <v>-17.973856209150</v>
       </c>
       <c r="M21" s="18">
-        <v>-47.477064220183</v>
+        <v>-45.905172413793</v>
       </c>
       <c r="N21" s="18">
-        <v>-90.043478260869</v>
+        <v>-89.846278317152</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="15">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
-        <v>2</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="14">
+        <v>0</v>
       </c>
       <c r="I22" s="15">
         <v>7</v>
       </c>
       <c r="J22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="14">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="L22" s="14">
         <v>16.666666666666</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="D24" s="15">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E24" s="14">
-        <v>21.875</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="F24" s="15">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G24" s="15">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H24" s="14">
-        <v>-22.962962962963</v>
+        <v>-28.057553956834</v>
       </c>
       <c r="I24" s="15">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="J24" s="15">
-        <v>367</v>
+        <v>396</v>
       </c>
       <c r="K24" s="14">
-        <v>-28.610354223433</v>
+        <v>-29.292929292929</v>
       </c>
       <c r="L24" s="14">
-        <v>-44.957983193277</v>
+        <v>-44.333996023856</v>
       </c>
       <c r="M24" s="14">
-        <v>-7.420494699646</v>
+        <v>-7.284768211920</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E25" s="14">
-        <v>-62.5</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="F25" s="15">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G25" s="15">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H25" s="14">
-        <v>-60.526315789473</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I25" s="15">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J25" s="15">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="K25" s="14">
-        <v>-65</v>
+        <v>-64.516129032258</v>
       </c>
       <c r="L25" s="14">
-        <v>-75.524475524475</v>
+        <v>-74.671052631578</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D26" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E26" s="14">
-        <v>-9.523809523809</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="F26" s="15">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G26" s="15">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="H26" s="14">
-        <v>20.338983050847</v>
+        <v>-10.447761194029</v>
       </c>
       <c r="I26" s="15">
+        <v>180</v>
+      </c>
+      <c r="J26" s="15">
         <v>167</v>
       </c>
-      <c r="J26" s="15">
-        <v>145</v>
-      </c>
       <c r="K26" s="14">
-        <v>15.172413793103</v>
+        <v>7.784431137724</v>
       </c>
       <c r="L26" s="14">
-        <v>3.726708074534</v>
+        <v>5.263157894736</v>
       </c>
       <c r="M26" s="14">
-        <v>-8.743169398907</v>
+        <v>-5.759162303664</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,7 +1388,7 @@
         <v>20</v>
       </c>
       <c r="D27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="14">
         <v>-100</v>
@@ -1397,7 +1397,7 @@
         <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1406,13 +1406,13 @@
         <v>2</v>
       </c>
       <c r="J27" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K27" s="14">
-        <v>-71.428571428571</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="L27" s="14">
-        <v>-71.428571428571</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" s="15">
         <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
         <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J28" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="14">
-        <v>55.555555555555</v>
+        <v>20</v>
       </c>
       <c r="L28" s="14">
-        <v>-26.315789473684</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N29" s="14">
-        <v>-92.857142857142</v>
+        <v>-93.103448275862</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-83.333333333333</v>
       </c>
       <c r="N30" s="14">
-        <v>-95.454545454545</v>
+        <v>-95.652173913043</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1560,11 +1560,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="15">
         <v>1</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="15">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="15">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="15">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-070pct.xlsx
+++ b/data/source/weekly/cs-en-us-070pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -895,17 +895,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>2</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="14">
         <v>-100</v>
@@ -920,13 +920,13 @@
         <v>-71.428571428571</v>
       </c>
       <c r="L15" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M15" s="14">
         <v>-60</v>
       </c>
       <c r="N15" s="14">
-        <v>-93.939393939393</v>
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="14">
-        <v>-33.333333333333</v>
+        <v>-80</v>
       </c>
       <c r="F16" s="15">
         <v>4</v>
       </c>
       <c r="G16" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H16" s="14">
-        <v>-63.636363636363</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="I16" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J16" s="15">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K16" s="14">
-        <v>-44</v>
+        <v>-47.272727272727</v>
       </c>
       <c r="L16" s="14">
-        <v>-36.363636363636</v>
+        <v>-38.297872340425</v>
       </c>
       <c r="M16" s="14">
-        <v>-72.815533980582</v>
+        <v>-73.148148148148</v>
       </c>
       <c r="N16" s="14">
-        <v>-95.087719298245</v>
+        <v>-95.142378559464</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E17" s="14">
-        <v>-62.5</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F17" s="15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G17" s="15">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H17" s="14">
-        <v>-58.490566037735</v>
+        <v>-60.344827586206</v>
       </c>
       <c r="I17" s="15">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="J17" s="15">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="K17" s="14">
-        <v>-50.381679389313</v>
+        <v>-50.344827586206</v>
       </c>
       <c r="L17" s="14">
         <v>0</v>
       </c>
       <c r="M17" s="14">
-        <v>-31.578947368421</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="N17" s="14">
-        <v>-68.446601941747</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E18" s="14">
-        <v>100</v>
+        <v>-60</v>
       </c>
       <c r="F18" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G18" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H18" s="14">
-        <v>-61.904761904761</v>
+        <v>-60.869565217391</v>
       </c>
       <c r="I18" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J18" s="15">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K18" s="14">
-        <v>-42.105263157894</v>
+        <v>-44.186046511627</v>
       </c>
       <c r="L18" s="14">
-        <v>-38.888888888888</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="M18" s="14">
-        <v>-63.333333333333</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="N18" s="14">
-        <v>-97.260273972602</v>
+        <v>-97.179788484136</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" s="15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F19" s="15">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G19" s="15">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H19" s="14">
-        <v>14.285714285714</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I19" s="15">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="J19" s="15">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="K19" s="14">
-        <v>-0.884955752212</v>
+        <v>2.521008403361</v>
       </c>
       <c r="L19" s="14">
-        <v>-10.4</v>
+        <v>-11.594202898550</v>
       </c>
       <c r="M19" s="14">
-        <v>-20.567375886524</v>
+        <v>-21.794871794871</v>
       </c>
       <c r="N19" s="14">
-        <v>-57.575757575757</v>
+        <v>-58.361774744027</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>3</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>-25</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G20" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H20" s="14">
-        <v>-50</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="I20" s="15">
         <v>22</v>
       </c>
       <c r="J20" s="15">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K20" s="14">
-        <v>-24.137931034482</v>
+        <v>-29.032258064516</v>
       </c>
       <c r="L20" s="14">
-        <v>-31.25</v>
+        <v>-37.142857142857</v>
       </c>
       <c r="M20" s="14">
-        <v>-61.403508771929</v>
+        <v>-63.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.239316239316</v>
+        <v>-96.594427244582</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E21" s="18">
-        <v>-30.555555555555</v>
+        <v>-43.75</v>
       </c>
       <c r="F21" s="17">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G21" s="17">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H21" s="18">
-        <v>-41.428571428571</v>
+        <v>-45.517241379310</v>
       </c>
       <c r="I21" s="17">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="J21" s="17">
-        <v>368</v>
+        <v>400</v>
       </c>
       <c r="K21" s="18">
-        <v>-31.793478260869</v>
+        <v>-32.25</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.973856209150</v>
+        <v>-19.104477611940</v>
       </c>
       <c r="M21" s="18">
-        <v>-45.905172413793</v>
+        <v>-46.123260437375</v>
       </c>
       <c r="N21" s="18">
-        <v>-89.846278317152</v>
+        <v>-89.773584905660</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
         <v>1</v>
@@ -1198,19 +1198,19 @@
         <v>0</v>
       </c>
       <c r="I22" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J22" s="15">
         <v>2</v>
       </c>
       <c r="K22" s="14">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="L22" s="14">
-        <v>16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M22" s="14">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D24" s="15">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E24" s="14">
-        <v>-37.931034482758</v>
+        <v>75</v>
       </c>
       <c r="F24" s="15">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="G24" s="15">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="H24" s="14">
-        <v>-28.057553956834</v>
+        <v>-4.032258064516</v>
       </c>
       <c r="I24" s="15">
-        <v>280</v>
+        <v>321</v>
       </c>
       <c r="J24" s="15">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="K24" s="14">
-        <v>-29.292929292929</v>
+        <v>-23.571428571428</v>
       </c>
       <c r="L24" s="14">
-        <v>-44.333996023856</v>
+        <v>-40.223463687150</v>
       </c>
       <c r="M24" s="14">
-        <v>-7.284768211920</v>
+        <v>-0.925925925925</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D25" s="15">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E25" s="14">
-        <v>-58.823529411764</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F25" s="15">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G25" s="15">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="H25" s="14">
-        <v>-63.636363636363</v>
+        <v>-48.484848484848</v>
       </c>
       <c r="I25" s="15">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J25" s="15">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="K25" s="14">
-        <v>-64.516129032258</v>
+        <v>-60.526315789473</v>
       </c>
       <c r="L25" s="14">
-        <v>-74.671052631578</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E26" s="14">
-        <v>-40.909090909090</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F26" s="15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G26" s="15">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H26" s="14">
-        <v>-10.447761194029</v>
+        <v>-21.875</v>
       </c>
       <c r="I26" s="15">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="J26" s="15">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="K26" s="14">
-        <v>7.784431137724</v>
+        <v>4.494382022471</v>
       </c>
       <c r="L26" s="14">
-        <v>5.263157894736</v>
+        <v>1.639344262295</v>
       </c>
       <c r="M26" s="14">
-        <v>-5.759162303664</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,17 +1387,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>2</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1412,7 +1412,7 @@
         <v>-77.777777777777</v>
       </c>
       <c r="L27" s="14">
-        <v>-77.777777777777</v>
+        <v>-80</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="15">
         <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="I28" s="15">
         <v>12</v>
       </c>
       <c r="J28" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K28" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L28" s="14">
-        <v>-36.842105263157</v>
+        <v>-40</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1493,14 +1493,14 @@
       <c r="K29" s="14">
         <v>0</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="14">
+        <v>100</v>
       </c>
       <c r="M29" s="14">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="N29" s="14">
-        <v>-93.103448275862</v>
+        <v>-93.939393939393</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1534,14 +1534,14 @@
       <c r="K30" s="14">
         <v>-50</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="14">
+        <v>0</v>
       </c>
       <c r="M30" s="14">
-        <v>-83.333333333333</v>
+        <v>-87.5</v>
       </c>
       <c r="N30" s="14">
-        <v>-95.652173913043</v>
+        <v>-96.296296296296</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>2</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="15">
+        <v>2</v>
+      </c>
+      <c r="H31" s="14">
+        <v>-100</v>
       </c>
       <c r="I31" s="15">
         <v>1</v>
       </c>
       <c r="J31" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K31" s="14">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="L31" s="14">
         <v>-66.666666666666</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="15">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-070pct.xlsx
+++ b/data/source/weekly/cs-en-us-070pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -914,19 +914,19 @@
         <v>2</v>
       </c>
       <c r="J15" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" s="14">
+        <v>-75</v>
+      </c>
+      <c r="L15" s="14">
         <v>-71.428571428571</v>
-      </c>
-      <c r="L15" s="14">
-        <v>-60</v>
       </c>
       <c r="M15" s="14">
         <v>-60</v>
       </c>
       <c r="N15" s="14">
-        <v>-94.444444444444</v>
+        <v>-94.736842105263</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="15">
         <v>4</v>
       </c>
       <c r="G16" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" s="14">
-        <v>-69.230769230769</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I16" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J16" s="15">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K16" s="14">
-        <v>-47.272727272727</v>
+        <v>-48.275862068965</v>
       </c>
       <c r="L16" s="14">
-        <v>-38.297872340425</v>
+        <v>-40</v>
       </c>
       <c r="M16" s="14">
-        <v>-73.148148148148</v>
+        <v>-74.137931034482</v>
       </c>
       <c r="N16" s="14">
-        <v>-95.142378559464</v>
+        <v>-95.230524642289</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D17" s="15">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E17" s="14">
-        <v>-57.142857142857</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G17" s="15">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H17" s="14">
-        <v>-60.344827586206</v>
+        <v>-56.140350877193</v>
       </c>
       <c r="I17" s="15">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="J17" s="15">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="K17" s="14">
-        <v>-50.344827586206</v>
+        <v>-47.402597402597</v>
       </c>
       <c r="L17" s="14">
-        <v>0</v>
+        <v>6.578947368421</v>
       </c>
       <c r="M17" s="14">
-        <v>-31.428571428571</v>
+        <v>-26.363636363636</v>
       </c>
       <c r="N17" s="14">
-        <v>-66.666666666666</v>
+        <v>-65.384615384615</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>-60</v>
       </c>
       <c r="F18" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H18" s="14">
-        <v>-60.869565217391</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J18" s="15">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K18" s="14">
-        <v>-44.186046511627</v>
+        <v>-43.75</v>
       </c>
       <c r="L18" s="14">
-        <v>-36.842105263157</v>
+        <v>-32.5</v>
       </c>
       <c r="M18" s="14">
-        <v>-63.636363636363</v>
+        <v>-63.513513513513</v>
       </c>
       <c r="N18" s="14">
-        <v>-97.179788484136</v>
+        <v>-97.032967032967</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
         <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G19" s="15">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H19" s="14">
-        <v>9.090909090909</v>
+        <v>27.586206896551</v>
       </c>
       <c r="I19" s="15">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J19" s="15">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="K19" s="14">
-        <v>2.521008403361</v>
+        <v>4</v>
       </c>
       <c r="L19" s="14">
-        <v>-11.594202898550</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M19" s="14">
-        <v>-21.794871794871</v>
+        <v>-24.418604651162</v>
       </c>
       <c r="N19" s="14">
-        <v>-58.361774744027</v>
+        <v>-60.486322188449</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>3</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H20" s="14">
-        <v>-53.333333333333</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="I20" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J20" s="15">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K20" s="14">
-        <v>-29.032258064516</v>
+        <v>-26.470588235294</v>
       </c>
       <c r="L20" s="14">
-        <v>-37.142857142857</v>
+        <v>-32.432432432432</v>
       </c>
       <c r="M20" s="14">
-        <v>-63.333333333333</v>
+        <v>-60.317460317460</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.594427244582</v>
+        <v>-96.508379888268</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>-43.75</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="F21" s="17">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G21" s="17">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H21" s="18">
-        <v>-45.517241379310</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I21" s="17">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="J21" s="17">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="K21" s="18">
-        <v>-32.25</v>
+        <v>-30.913348946135</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.104477611940</v>
+        <v>-18.055555555555</v>
       </c>
       <c r="M21" s="18">
-        <v>-46.123260437375</v>
+        <v>-45.672191528545</v>
       </c>
       <c r="N21" s="18">
-        <v>-89.773584905660</v>
+        <v>-89.714086471408</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D24" s="15">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E24" s="14">
-        <v>75</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="F24" s="15">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G24" s="15">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="H24" s="14">
-        <v>-4.032258064516</v>
+        <v>7.964601769911</v>
       </c>
       <c r="I24" s="15">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="J24" s="15">
-        <v>420</v>
+        <v>448</v>
       </c>
       <c r="K24" s="14">
-        <v>-23.571428571428</v>
+        <v>-23.214285714285</v>
       </c>
       <c r="L24" s="14">
-        <v>-40.223463687150</v>
+        <v>-39.649122807017</v>
       </c>
       <c r="M24" s="14">
-        <v>-0.925925925925</v>
+        <v>1.176470588235</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E25" s="14">
-        <v>18.181818181818</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F25" s="15">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G25" s="15">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="H25" s="14">
-        <v>-48.484848484848</v>
+        <v>-46.551724137931</v>
       </c>
       <c r="I25" s="15">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J25" s="15">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="K25" s="14">
-        <v>-60.526315789473</v>
+        <v>-60.743801652892</v>
       </c>
       <c r="L25" s="14">
-        <v>-72.727272727272</v>
+        <v>-72.934472934472</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D26" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E26" s="14">
-        <v>-45.454545454545</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G26" s="15">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H26" s="14">
-        <v>-21.875</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="I26" s="15">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="J26" s="15">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="K26" s="14">
-        <v>4.494382022471</v>
+        <v>4.736842105263</v>
       </c>
       <c r="L26" s="14">
-        <v>1.639344262295</v>
+        <v>3.108808290155</v>
       </c>
       <c r="M26" s="14">
-        <v>-8.823529411764</v>
+        <v>-6.572769953051</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1406,13 +1406,13 @@
         <v>2</v>
       </c>
       <c r="J27" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" s="14">
-        <v>-77.777777777777</v>
+        <v>-80</v>
       </c>
       <c r="L27" s="14">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,10 +1429,10 @@
         <v>1</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F28" s="15">
         <v>3</v>
@@ -1444,16 +1444,16 @@
         <v>-40</v>
       </c>
       <c r="I28" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J28" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="14">
         <v>0</v>
       </c>
       <c r="L28" s="14">
-        <v>-40</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="15">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,40 +1475,40 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="15">
+      <c r="F29" s="15">
         <v>1</v>
       </c>
-      <c r="H29" s="14">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="15">
         <v>2</v>
       </c>
       <c r="K29" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L29" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M29" s="14">
-        <v>-80</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="N29" s="14">
-        <v>-93.939393939393</v>
+        <v>-91.428571428571</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="15">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,32 +1516,32 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="15">
+      <c r="F30" s="15">
         <v>1</v>
       </c>
-      <c r="H30" s="14">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="15">
         <v>2</v>
       </c>
       <c r="K30" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L30" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30" s="14">
-        <v>-87.5</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="N30" s="14">
-        <v>-96.296296296296</v>
+        <v>-93.103448275862</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>2</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-070pct.xlsx
+++ b/data/source/weekly/cs-en-us-070pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -892,55 +892,55 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="15">
+      <c r="C15" s="15">
         <v>1</v>
       </c>
-      <c r="E15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
+        <v>1</v>
       </c>
       <c r="G15" s="15">
         <v>3</v>
       </c>
       <c r="H15" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15" s="15">
         <v>8</v>
       </c>
       <c r="K15" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="14">
-        <v>-71.428571428571</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M15" s="14">
-        <v>-60</v>
+        <v>-20</v>
       </c>
       <c r="N15" s="14">
-        <v>-94.736842105263</v>
+        <v>-90.243902439024</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="15">
         <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
         <v>4</v>
@@ -955,19 +955,19 @@
         <v>30</v>
       </c>
       <c r="J16" s="15">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K16" s="14">
-        <v>-48.275862068965</v>
+        <v>-50.819672131147</v>
       </c>
       <c r="L16" s="14">
-        <v>-40</v>
+        <v>-43.396226415094</v>
       </c>
       <c r="M16" s="14">
-        <v>-74.137931034482</v>
+        <v>-75</v>
       </c>
       <c r="N16" s="14">
-        <v>-95.230524642289</v>
+        <v>-95.412844036697</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" s="15">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="F17" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G17" s="15">
         <v>57</v>
       </c>
       <c r="H17" s="14">
-        <v>-56.140350877193</v>
+        <v>-50.877192982456</v>
       </c>
       <c r="I17" s="15">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J17" s="15">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="K17" s="14">
-        <v>-47.402597402597</v>
+        <v>-48.837209302325</v>
       </c>
       <c r="L17" s="14">
-        <v>6.578947368421</v>
+        <v>7.317073170731</v>
       </c>
       <c r="M17" s="14">
-        <v>-26.363636363636</v>
+        <v>-24.786324786324</v>
       </c>
       <c r="N17" s="14">
-        <v>-65.384615384615</v>
+        <v>-64.658634538152</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
+        <v>1</v>
+      </c>
+      <c r="D18" s="15">
         <v>2</v>
       </c>
-      <c r="D18" s="15">
-        <v>5</v>
-      </c>
       <c r="E18" s="14">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G18" s="15">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H18" s="14">
-        <v>-58.333333333333</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I18" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J18" s="15">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K18" s="14">
-        <v>-43.75</v>
+        <v>-44</v>
       </c>
       <c r="L18" s="14">
-        <v>-32.5</v>
+        <v>-31.707317073170</v>
       </c>
       <c r="M18" s="14">
-        <v>-63.513513513513</v>
+        <v>-65.853658536585</v>
       </c>
       <c r="N18" s="14">
-        <v>-97.032967032967</v>
+        <v>-97.098445595854</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="15">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E19" s="14">
-        <v>33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="F19" s="15">
         <v>37</v>
       </c>
       <c r="G19" s="15">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="H19" s="14">
-        <v>27.586206896551</v>
+        <v>0</v>
       </c>
       <c r="I19" s="15">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="J19" s="15">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="K19" s="14">
-        <v>4</v>
+        <v>-0.714285714285</v>
       </c>
       <c r="L19" s="14">
-        <v>-13.333333333333</v>
+        <v>-15.757575757575</v>
       </c>
       <c r="M19" s="14">
-        <v>-24.418604651162</v>
+        <v>-24.864864864864</v>
       </c>
       <c r="N19" s="14">
-        <v>-60.486322188449</v>
+        <v>-60.398860398860</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>3</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="15">
         <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G20" s="15">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H20" s="14">
-        <v>-52.941176470588</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="15">
         <v>25</v>
       </c>
       <c r="J20" s="15">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K20" s="14">
-        <v>-26.470588235294</v>
+        <v>-32.432432432432</v>
       </c>
       <c r="L20" s="14">
         <v>-32.432432432432</v>
       </c>
       <c r="M20" s="14">
-        <v>-60.317460317460</v>
+        <v>-62.121212121212</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.508379888268</v>
+        <v>-96.765847347994</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>-14.814814814814</v>
+        <v>-56.097560975609</v>
       </c>
       <c r="F21" s="17">
         <v>84</v>
       </c>
       <c r="G21" s="17">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H21" s="18">
-        <v>-41.666666666666</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="I21" s="17">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="J21" s="17">
-        <v>427</v>
+        <v>468</v>
       </c>
       <c r="K21" s="18">
-        <v>-30.913348946135</v>
+        <v>-32.905982905982</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.055555555555</v>
+        <v>-18.441558441558</v>
       </c>
       <c r="M21" s="18">
-        <v>-45.672191528545</v>
+        <v>-45.674740484429</v>
       </c>
       <c r="N21" s="18">
-        <v>-89.714086471408</v>
+        <v>-89.688013136289</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,14 +1188,14 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="15">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="15">
         <v>8</v>
@@ -1207,7 +1207,7 @@
         <v>300</v>
       </c>
       <c r="L22" s="14">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M22" s="14">
         <v>-20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D24" s="15">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E24" s="14">
-        <v>-10.714285714285</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F24" s="15">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="G24" s="15">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="H24" s="14">
-        <v>7.964601769911</v>
+        <v>5.050505050505</v>
       </c>
       <c r="I24" s="15">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="J24" s="15">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="K24" s="14">
-        <v>-23.214285714285</v>
+        <v>-21.673819742489</v>
       </c>
       <c r="L24" s="14">
-        <v>-39.649122807017</v>
+        <v>-40.065681444991</v>
       </c>
       <c r="M24" s="14">
-        <v>1.176470588235</v>
+        <v>0</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" s="15">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E25" s="14">
-        <v>-57.142857142857</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F25" s="15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G25" s="15">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H25" s="14">
-        <v>-46.551724137931</v>
+        <v>-37.254901960784</v>
       </c>
       <c r="I25" s="15">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="J25" s="15">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="K25" s="14">
-        <v>-60.743801652892</v>
+        <v>-59.362549800796</v>
       </c>
       <c r="L25" s="14">
-        <v>-72.934472934472</v>
+        <v>-72.944297082228</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>16</v>
+      </c>
+      <c r="D26" s="15">
         <v>13</v>
       </c>
-      <c r="D26" s="15">
-        <v>12</v>
-      </c>
       <c r="E26" s="14">
-        <v>8.333333333333</v>
+        <v>23.076923076923</v>
       </c>
       <c r="F26" s="15">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G26" s="15">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="H26" s="14">
-        <v>-22.727272727272</v>
+        <v>-17.241379310344</v>
       </c>
       <c r="I26" s="15">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="J26" s="15">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="K26" s="14">
-        <v>4.736842105263</v>
+        <v>5.418719211822</v>
       </c>
       <c r="L26" s="14">
-        <v>3.108808290155</v>
+        <v>5.940594059405</v>
       </c>
       <c r="M26" s="14">
-        <v>-6.572769953051</v>
+        <v>-4.888888888888</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="15">
         <v>1</v>
       </c>
       <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="F27" s="15">
+        <v>1</v>
       </c>
       <c r="G27" s="15">
         <v>4</v>
       </c>
       <c r="H27" s="14">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J27" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K27" s="14">
-        <v>-80</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="L27" s="14">
-        <v>-83.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H28" s="14">
-        <v>-40</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I28" s="15">
         <v>13</v>
       </c>
       <c r="J28" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K28" s="14">
-        <v>0</v>
+        <v>-18.75</v>
       </c>
       <c r="L28" s="14">
-        <v>-40.909090909090</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,32 +1466,32 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="15">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="E29" s="14">
+        <v>-100</v>
       </c>
       <c r="F29" s="15">
         <v>1</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="15">
+        <v>1</v>
+      </c>
+      <c r="H29" s="14">
+        <v>0</v>
       </c>
       <c r="I29" s="15">
         <v>3</v>
       </c>
       <c r="J29" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L29" s="14">
         <v>200</v>
@@ -1500,39 +1500,39 @@
         <v>-72.727272727272</v>
       </c>
       <c r="N29" s="14">
-        <v>-91.428571428571</v>
+        <v>-91.891891891891</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="15">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="E30" s="14">
+        <v>-100</v>
       </c>
       <c r="F30" s="15">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="15">
+        <v>1</v>
+      </c>
+      <c r="H30" s="14">
+        <v>0</v>
       </c>
       <c r="I30" s="15">
         <v>2</v>
       </c>
       <c r="J30" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L30" s="14">
         <v>100</v>
@@ -1541,7 +1541,7 @@
         <v>-77.777777777777</v>
       </c>
       <c r="N30" s="14">
-        <v>-93.103448275862</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1576,7 +1576,7 @@
         <v>-83.333333333333</v>
       </c>
       <c r="L31" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-070pct.xlsx
+++ b/data/source/weekly/cs-en-us-070pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -893,81 +893,81 @@
         <v>22</v>
       </c>
       <c r="C15" s="15">
-        <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D15" s="15">
+        <v>3</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-33.333333333333</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="14">
-        <v>-66.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="I15" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J15" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K15" s="14">
-        <v>-50</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L15" s="14">
-        <v>-42.857142857142</v>
+        <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="N15" s="14">
-        <v>-90.243902439024</v>
+        <v>-83.720930232558</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>1</v>
       </c>
       <c r="D16" s="15">
         <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="15">
         <v>14</v>
       </c>
       <c r="H16" s="14">
-        <v>-71.428571428571</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="I16" s="15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J16" s="15">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K16" s="14">
-        <v>-50.819672131147</v>
+        <v>-51.5625</v>
       </c>
       <c r="L16" s="14">
-        <v>-43.396226415094</v>
+        <v>-46.551724137931</v>
       </c>
       <c r="M16" s="14">
-        <v>-75</v>
+        <v>-75.590551181102</v>
       </c>
       <c r="N16" s="14">
-        <v>-95.412844036697</v>
+        <v>-95.513748191027</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E17" s="14">
-        <v>-61.111111111111</v>
+        <v>-62.5</v>
       </c>
       <c r="F17" s="15">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G17" s="15">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="H17" s="14">
-        <v>-50.877192982456</v>
+        <v>-51.020408163265</v>
       </c>
       <c r="I17" s="15">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J17" s="15">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="K17" s="14">
-        <v>-48.837209302325</v>
+        <v>-48.888888888888</v>
       </c>
       <c r="L17" s="14">
-        <v>7.317073170731</v>
+        <v>8.235294117647</v>
       </c>
       <c r="M17" s="14">
-        <v>-24.786324786324</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>-64.658634538152</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G18" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H18" s="14">
-        <v>-38.461538461538</v>
+        <v>-60</v>
       </c>
       <c r="I18" s="15">
         <v>28</v>
       </c>
       <c r="J18" s="15">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K18" s="14">
-        <v>-44</v>
+        <v>-47.169811320754</v>
       </c>
       <c r="L18" s="14">
-        <v>-31.707317073170</v>
+        <v>-34.883720930232</v>
       </c>
       <c r="M18" s="14">
-        <v>-65.853658536585</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="N18" s="14">
-        <v>-97.098445595854</v>
+        <v>-97.252208047105</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14">
-        <v>-40</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F19" s="15">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G19" s="15">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H19" s="14">
-        <v>0</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I19" s="15">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="J19" s="15">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="K19" s="14">
-        <v>-0.714285714285</v>
+        <v>-0.680272108843</v>
       </c>
       <c r="L19" s="14">
-        <v>-15.757575757575</v>
+        <v>-19.780219780219</v>
       </c>
       <c r="M19" s="14">
-        <v>-24.864864864864</v>
+        <v>-25.888324873096</v>
       </c>
       <c r="N19" s="14">
-        <v>-60.398860398860</v>
+        <v>-60.646900269541</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>1</v>
       </c>
       <c r="D20" s="15">
         <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G20" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H20" s="14">
-        <v>-50</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I20" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J20" s="15">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K20" s="14">
-        <v>-32.432432432432</v>
+        <v>-35</v>
       </c>
       <c r="L20" s="14">
-        <v>-32.432432432432</v>
+        <v>-39.534883720930</v>
       </c>
       <c r="M20" s="14">
-        <v>-62.121212121212</v>
+        <v>-63.380281690140</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.765847347994</v>
+        <v>-96.897374701670</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>-56.097560975609</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F21" s="17">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G21" s="17">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="H21" s="18">
-        <v>-38.235294117647</v>
+        <v>-43.307086614173</v>
       </c>
       <c r="I21" s="17">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="J21" s="17">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="K21" s="18">
-        <v>-32.905982905982</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.441558441558</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="M21" s="18">
-        <v>-45.674740484429</v>
+        <v>-46.428571428571</v>
       </c>
       <c r="N21" s="18">
-        <v>-89.688013136289</v>
+        <v>-89.858635525507</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1188,29 +1188,29 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="15">
+      <c r="F22" s="15">
         <v>1</v>
       </c>
-      <c r="H22" s="14">
-        <v>-100</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J22" s="15">
         <v>2</v>
       </c>
       <c r="K22" s="14">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="L22" s="14">
-        <v>14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="M22" s="14">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D24" s="15">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E24" s="14">
-        <v>22.222222222222</v>
+        <v>0</v>
       </c>
       <c r="F24" s="15">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="G24" s="15">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H24" s="14">
-        <v>5.050505050505</v>
+        <v>15.533980582524</v>
       </c>
       <c r="I24" s="15">
-        <v>365</v>
+        <v>398</v>
       </c>
       <c r="J24" s="15">
-        <v>466</v>
+        <v>499</v>
       </c>
       <c r="K24" s="14">
-        <v>-21.673819742489</v>
+        <v>-20.240480961923</v>
       </c>
       <c r="L24" s="14">
-        <v>-40.065681444991</v>
+        <v>-36.925515055467</v>
       </c>
       <c r="M24" s="14">
-        <v>0</v>
+        <v>3.108808290155</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D25" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E25" s="14">
-        <v>-22.222222222222</v>
+        <v>-10</v>
       </c>
       <c r="F25" s="15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G25" s="15">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H25" s="14">
-        <v>-37.254901960784</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="I25" s="15">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="J25" s="15">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="K25" s="14">
-        <v>-59.362549800796</v>
+        <v>-57.471264367816</v>
       </c>
       <c r="L25" s="14">
-        <v>-72.944297082228</v>
+        <v>-71.683673469387</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D26" s="15">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E26" s="14">
-        <v>23.076923076923</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="F26" s="15">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G26" s="15">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H26" s="14">
-        <v>-17.241379310344</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="I26" s="15">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="J26" s="15">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="K26" s="14">
-        <v>5.418719211822</v>
+        <v>3.636363636363</v>
       </c>
       <c r="L26" s="14">
-        <v>5.940594059405</v>
+        <v>7.042253521126</v>
       </c>
       <c r="M26" s="14">
-        <v>-4.888888888888</v>
+        <v>-6.172839506172</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="14">
-        <v>-75</v>
+        <v>-40</v>
       </c>
       <c r="I27" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J27" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K27" s="14">
-        <v>-63.636363636363</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="14">
-        <v>-66.666666666666</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="15">
+      <c r="E28" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="15">
         <v>3</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F28" s="15">
-        <v>4</v>
       </c>
       <c r="G28" s="15">
         <v>7</v>
       </c>
       <c r="H28" s="14">
-        <v>-42.857142857142</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I28" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J28" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" s="14">
-        <v>-18.75</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="L28" s="14">
-        <v>-43.478260869565</v>
+        <v>-52</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="15">
-        <v>1</v>
-      </c>
-      <c r="E29" s="14">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="15">
         <v>1</v>
@@ -1500,7 +1500,7 @@
         <v>-72.727272727272</v>
       </c>
       <c r="N29" s="14">
-        <v>-91.891891891891</v>
+        <v>-92.682926829268</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="15">
-        <v>1</v>
-      </c>
-      <c r="E30" s="14">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="15">
         <v>1</v>
@@ -1541,7 +1541,7 @@
         <v>-77.777777777777</v>
       </c>
       <c r="N30" s="14">
-        <v>-93.333333333333</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="15">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-070pct.xlsx
+++ b/data/source/weekly/cs-en-us-070pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="15">
-        <v>2</v>
-      </c>
-      <c r="D15" s="15">
-        <v>3</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-33.333333333333</v>
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="15">
         <v>4</v>
       </c>
       <c r="H15" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="15">
         <v>11</v>
       </c>
       <c r="K15" s="14">
-        <v>-36.363636363636</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N15" s="14">
-        <v>-83.720930232558</v>
+        <v>-81.395348837209</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G16" s="15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H16" s="14">
-        <v>-78.571428571428</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="I16" s="15">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J16" s="15">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K16" s="14">
-        <v>-51.5625</v>
+        <v>-48.529411764705</v>
       </c>
       <c r="L16" s="14">
-        <v>-46.551724137931</v>
+        <v>-45.3125</v>
       </c>
       <c r="M16" s="14">
-        <v>-75.590551181102</v>
+        <v>-73.484848484848</v>
       </c>
       <c r="N16" s="14">
-        <v>-95.513748191027</v>
+        <v>-95.225102319236</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D17" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="14">
-        <v>-62.5</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G17" s="15">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H17" s="14">
-        <v>-51.020408163265</v>
+        <v>-40.476190476190</v>
       </c>
       <c r="I17" s="15">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="J17" s="15">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="K17" s="14">
-        <v>-48.888888888888</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="L17" s="14">
-        <v>8.235294117647</v>
+        <v>12.5</v>
       </c>
       <c r="M17" s="14">
-        <v>-23.333333333333</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="N17" s="14">
-        <v>-66.666666666666</v>
+        <v>-66.440677966101</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G18" s="15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H18" s="14">
-        <v>-60</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="I18" s="15">
         <v>28</v>
       </c>
       <c r="J18" s="15">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K18" s="14">
-        <v>-47.169811320754</v>
+        <v>-50</v>
       </c>
       <c r="L18" s="14">
-        <v>-34.883720930232</v>
+        <v>-37.777777777777</v>
       </c>
       <c r="M18" s="14">
-        <v>-69.230769230769</v>
+        <v>-71.134020618556</v>
       </c>
       <c r="N18" s="14">
-        <v>-97.252208047105</v>
+        <v>-97.363465160075</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E19" s="14">
-        <v>14.285714285714</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G19" s="15">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H19" s="14">
-        <v>-5.882352941176</v>
+        <v>-2.5</v>
       </c>
       <c r="I19" s="15">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="J19" s="15">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="K19" s="14">
-        <v>-0.680272108843</v>
+        <v>1.257861635220</v>
       </c>
       <c r="L19" s="14">
-        <v>-19.780219780219</v>
+        <v>-15.706806282722</v>
       </c>
       <c r="M19" s="14">
-        <v>-25.888324873096</v>
+        <v>-22.596153846153</v>
       </c>
       <c r="N19" s="14">
-        <v>-60.646900269541</v>
+        <v>-59.033078880407</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>-66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="F20" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15">
         <v>11</v>
       </c>
       <c r="H20" s="14">
-        <v>-63.636363636363</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I20" s="15">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J20" s="15">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K20" s="14">
-        <v>-35</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L20" s="14">
-        <v>-39.534883720930</v>
+        <v>-38.775510204081</v>
       </c>
       <c r="M20" s="14">
-        <v>-63.380281690140</v>
+        <v>-59.459459459459</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.897374701670</v>
+        <v>-96.632996632996</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>-44.444444444444</v>
+        <v>3.571428571428</v>
       </c>
       <c r="F21" s="17">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G21" s="17">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H21" s="18">
-        <v>-43.307086614173</v>
+        <v>-30.894308943089</v>
       </c>
       <c r="I21" s="17">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="J21" s="17">
-        <v>495</v>
+        <v>523</v>
       </c>
       <c r="K21" s="18">
-        <v>-33.333333333333</v>
+        <v>-30.975143403441</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.052631578947</v>
+        <v>-18.876404494382</v>
       </c>
       <c r="M21" s="18">
-        <v>-46.428571428571</v>
+        <v>-44.204018547140</v>
       </c>
       <c r="N21" s="18">
-        <v>-89.858635525507</v>
+        <v>-89.484415962714</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" s="15">
         <v>2</v>
       </c>
       <c r="K22" s="14">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="L22" s="14">
-        <v>12.5</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M22" s="14">
-        <v>-10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D24" s="15">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E24" s="14">
-        <v>0</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="F24" s="15">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="G24" s="15">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H24" s="14">
-        <v>15.533980582524</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="I24" s="15">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="J24" s="15">
-        <v>499</v>
+        <v>530</v>
       </c>
       <c r="K24" s="14">
-        <v>-20.240480961923</v>
+        <v>-20</v>
       </c>
       <c r="L24" s="14">
-        <v>-36.925515055467</v>
+        <v>-35.660091047041</v>
       </c>
       <c r="M24" s="14">
-        <v>3.108808290155</v>
+        <v>3.163017031630</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D25" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E25" s="14">
-        <v>-10</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F25" s="15">
         <v>34</v>
       </c>
       <c r="G25" s="15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H25" s="14">
-        <v>-22.727272727272</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="I25" s="15">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="J25" s="15">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="K25" s="14">
-        <v>-57.471264367816</v>
+        <v>-55.109489051094</v>
       </c>
       <c r="L25" s="14">
-        <v>-71.683673469387</v>
+        <v>-69.704433497536</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D26" s="15">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>-11.764705882352</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F26" s="15">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G26" s="15">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H26" s="14">
-        <v>-5.660377358490</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I26" s="15">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="J26" s="15">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="K26" s="14">
-        <v>3.636363636363</v>
+        <v>5.240174672489</v>
       </c>
       <c r="L26" s="14">
-        <v>7.042253521126</v>
+        <v>6.637168141592</v>
       </c>
       <c r="M26" s="14">
-        <v>-6.172839506172</v>
+        <v>-8.015267175572</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="15">
-        <v>2</v>
-      </c>
-      <c r="D27" s="15">
-        <v>3</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-33.333333333333</v>
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="15">
         <v>5</v>
       </c>
       <c r="H27" s="14">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="I27" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="15">
         <v>14</v>
       </c>
       <c r="K27" s="14">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L27" s="14">
-        <v>-41.666666666666</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="C28" s="15">
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>-57.142857142857</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J28" s="15">
         <v>17</v>
       </c>
       <c r="K28" s="14">
-        <v>-29.411764705882</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="L28" s="14">
-        <v>-52</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>200</v>
       </c>
       <c r="M29" s="14">
-        <v>-72.727272727272</v>
+        <v>-75</v>
       </c>
       <c r="N29" s="14">
-        <v>-92.682926829268</v>
+        <v>-93.023255813953</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>100</v>
       </c>
       <c r="M30" s="14">
-        <v>-77.777777777777</v>
+        <v>-80</v>
       </c>
       <c r="N30" s="14">
-        <v>-93.75</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1560,11 +1560,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="15">
-        <v>2</v>
-      </c>
-      <c r="H31" s="14">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="15">
         <v>1</v>
@@ -1576,7 +1576,7 @@
         <v>-83.333333333333</v>
       </c>
       <c r="L31" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="15">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1626,7 +1626,7 @@
         <v>21</v>
       </c>
       <c r="I33" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>
